--- a/data/human/adult/validation/Scenarios/Hemorrhage/Hemorrhage.xlsx
+++ b/data/human/adult/validation/Scenarios/Hemorrhage/Hemorrhage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\Hemorrhage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachel.clipp/Projects/PulsePhysiologyEngine/data/human/adult/validation/Scenarios/Hemorrhage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769DE9BE-5BBA-4970-960A-3A4491490639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE80D1F2-F9FD-8941-AC3C-32434FCC50EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="760" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class1Femoral" sheetId="15" r:id="rId1"/>
@@ -472,13 +472,7 @@
     <t>25% Blood Loss</t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 3000, "Unit": "s" }}}}</t>
-  </si>
-  <si>
     <t>ActionCmpt</t>
-  </si>
-  <si>
-    <t>Run for 3000s.</t>
   </si>
   <si>
     <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 565, "Unit": "s" }}}}</t>
@@ -804,6 +798,12 @@
   </si>
   <si>
     <t>Run for 1500s.</t>
+  </si>
+  <si>
+    <t>Run for 20000s.</t>
+  </si>
+  <si>
+    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 20000, "Unit": "s" }}}}</t>
   </si>
 </sst>
 </file>
@@ -1485,19 +1485,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415C2FCE-0151-4310-828D-F5A5D79BC461}">
   <dimension ref="A1:AMJ32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>27</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -1583,9 +1583,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -1603,9 +1603,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1645,7 +1645,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -1677,7 +1677,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>2</v>
       </c>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>19</v>
       </c>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -2165,19 +2165,19 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04E6A3F-E106-3945-A9DD-82556D372646}">
   <dimension ref="A1:AMJ18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2195,9 +2195,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -2206,12 +2206,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -2263,9 +2263,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -2283,9 +2283,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -2303,9 +2303,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -2323,9 +2323,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -2341,7 +2341,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -2373,7 +2373,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8">
         <v>2</v>
       </c>
@@ -2469,19 +2469,19 @@
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>2</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
       <c r="G18" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>125</v>
@@ -2520,19 +2520,19 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26E90DC-EED0-F943-AC9A-DA7922187581}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2550,9 +2550,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -2566,7 +2566,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -2618,9 +2618,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -2638,9 +2638,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2668,7 +2668,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2678,7 +2678,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -2776,19 +2776,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -2825,19 +2825,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F482ED-E784-324D-BD37-BFE592C64201}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2855,9 +2855,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -2866,12 +2866,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -2923,9 +2923,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -2943,9 +2943,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2973,7 +2973,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2983,7 +2983,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3015,7 +3015,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3031,23 +3031,23 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -3081,19 +3081,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -3130,19 +3130,19 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4DD05FF-8930-A541-845A-6ACD5B6F713E}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -3160,9 +3160,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -3171,12 +3171,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -3228,9 +3228,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -3248,9 +3248,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3278,7 +3278,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -3288,7 +3288,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3320,7 +3320,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3336,23 +3336,23 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -3386,19 +3386,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -3435,19 +3435,19 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D50971-6CC3-724C-B02F-BDD1CA7924DF}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -3465,9 +3465,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -3476,12 +3476,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -3533,9 +3533,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -3553,9 +3553,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3583,7 +3583,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -3593,7 +3593,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3625,7 +3625,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3641,23 +3641,23 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -3691,19 +3691,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -3740,19 +3740,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86C4FC5C-674F-6743-9E54-39D7BCC969FF}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -3770,9 +3770,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -3781,12 +3781,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -3838,9 +3838,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -3858,9 +3858,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3888,7 +3888,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -3898,7 +3898,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3930,7 +3930,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3946,23 +3946,23 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -3996,19 +3996,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -4045,19 +4045,19 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A47E0F-918F-6B4E-BC7C-8144A14CD7C4}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -4075,9 +4075,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4086,12 +4086,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -4143,9 +4143,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>84</v>
@@ -4163,9 +4163,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4193,7 +4193,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4203,7 +4203,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -4235,7 +4235,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -4251,23 +4251,23 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -4301,19 +4301,19 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>125</v>
@@ -4350,19 +4350,19 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBCD6E5-DA97-7E41-B1E5-03FE61C76755}">
   <dimension ref="A1:AMJ13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -4380,9 +4380,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4391,12 +4391,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -4448,9 +4448,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -4468,9 +4468,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4498,7 +4498,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4508,7 +4508,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -4540,35 +4540,35 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="26"/>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H13" s="9"/>
     </row>
@@ -4600,19 +4600,19 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3492F5CA-AB1C-814E-ACA0-EBA6C7B473D7}">
   <dimension ref="A1:AMJ34"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -4630,9 +4630,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4641,12 +4641,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -4698,9 +4698,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -4718,9 +4718,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -4748,7 +4748,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -4758,7 +4758,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -4790,41 +4790,41 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="26"/>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -4842,39 +4842,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
       <c r="F15" s="26"/>
       <c r="G15" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
@@ -4900,9 +4900,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
@@ -4918,13 +4918,13 @@
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -4942,39 +4942,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="8">
         <v>3</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
       <c r="F20" s="26"/>
       <c r="G20" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="8">
         <v>3</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
       <c r="F21" s="23"/>
       <c r="G21" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
@@ -5000,9 +5000,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>48</v>
@@ -5018,13 +5018,13 @@
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -5042,39 +5042,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>4</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
       <c r="F25" s="26"/>
       <c r="G25" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>4</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
@@ -5100,9 +5100,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>48</v>
@@ -5118,13 +5118,13 @@
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -5142,23 +5142,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8">
         <v>4</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
       <c r="F30" s="26"/>
       <c r="G30" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="8">
         <v>4</v>
       </c>
@@ -5170,11 +5170,11 @@
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
@@ -5200,9 +5200,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="32" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>48</v>
@@ -5218,15 +5218,15 @@
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="32" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>48</v>
@@ -5242,10 +5242,10 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -5288,19 +5288,19 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C43238-B815-F04E-9AD6-088395AFC7A2}">
   <dimension ref="A1:AMJ19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -5318,9 +5318,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -5329,12 +5329,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -5386,9 +5386,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -5406,9 +5406,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -5436,7 +5436,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -5446,7 +5446,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -5478,39 +5478,39 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="26"/>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>2</v>
       </c>
@@ -5540,27 +5540,27 @@
       <c r="E15" s="25"/>
       <c r="F15" s="26"/>
       <c r="G15" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -5578,35 +5578,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>3</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
       <c r="F18" s="26"/>
       <c r="G18" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
       <c r="G19" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H19" s="9"/>
     </row>
@@ -5644,19 +5644,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB0DE949-96F2-4FF5-8FFB-07D9D12DF325}">
   <dimension ref="A1:AMJ32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -5674,7 +5674,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>54</v>
       </c>
@@ -5690,7 +5690,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -5742,9 +5742,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>57</v>
@@ -5762,9 +5762,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>58</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -5804,7 +5804,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -5836,7 +5836,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>2</v>
       </c>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>19</v>
       </c>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -6331,19 +6331,19 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5338BD-A665-B544-AD6C-5E2F4E9E7EC5}">
   <dimension ref="A1:AMJ18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -6361,9 +6361,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -6372,12 +6372,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>24</v>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>49</v>
@@ -6487,12 +6487,12 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
@@ -6505,7 +6505,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -6537,55 +6537,55 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="26"/>
       <c r="G12" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="56.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="56" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
       <c r="F13" s="26"/>
       <c r="G13" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -6603,39 +6603,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>2</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
       <c r="F16" s="26"/>
       <c r="G16" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" ht="60.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="61" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8">
         <v>2</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
       <c r="F17" s="26"/>
       <c r="G17" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>2</v>
       </c>
@@ -6684,19 +6684,19 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4D3527-BAF9-A848-A9FF-C5C5A6E174C1}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -6714,9 +6714,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -6725,12 +6725,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -6782,9 +6782,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
@@ -6802,9 +6802,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>93</v>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6832,7 +6832,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -6842,7 +6842,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -6874,23 +6874,23 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
       <c r="F12" s="26"/>
       <c r="G12" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -6924,12 +6924,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>1</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -6987,19 +6987,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941816A4-E7BA-914C-AD17-A1B29BE25C9A}">
   <dimension ref="A1:AMJ32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -7017,9 +7017,9 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -7028,12 +7028,12 @@
         <v>26</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -7085,9 +7085,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
@@ -7105,9 +7105,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>93</v>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>49</v>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
@@ -7163,12 +7163,12 @@
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>49</v>
@@ -7181,12 +7181,12 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>24</v>
@@ -7199,12 +7199,12 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
@@ -7217,12 +7217,12 @@
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -7235,12 +7235,12 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
@@ -7253,12 +7253,12 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
@@ -7271,12 +7271,12 @@
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>35</v>
@@ -7289,12 +7289,12 @@
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>35</v>
@@ -7307,12 +7307,12 @@
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>35</v>
@@ -7325,12 +7325,12 @@
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>35</v>
@@ -7343,12 +7343,12 @@
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>35</v>
@@ -7361,12 +7361,12 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>35</v>
@@ -7379,7 +7379,7 @@
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -7397,7 +7397,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>1</v>
       </c>
@@ -7411,12 +7411,12 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>1</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C24" s="23"/>
       <c r="D24" s="23"/>
@@ -7427,39 +7427,39 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>1</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
       <c r="G25" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>1</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8">
         <v>1</v>
       </c>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -7493,55 +7493,55 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8">
         <v>2</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
       <c r="G29" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8">
         <v>2</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
       <c r="G30" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8">
         <v>2</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8">
         <v>2</v>
       </c>
@@ -7604,19 +7604,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D528636C-F1B4-424F-9D9B-87019496D8B8}">
   <dimension ref="A1:AMJ35"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.5" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -7634,7 +7634,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>74</v>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -7702,9 +7702,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -7722,9 +7722,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -7742,9 +7742,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -7762,9 +7762,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -7780,7 +7780,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -7812,7 +7812,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="8">
         <v>2</v>
       </c>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>19</v>
       </c>
@@ -8357,19 +8357,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FBF74F-2F3D-48A7-8ACC-46AE74B2ED9E}">
   <dimension ref="A1:AMJ45"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -8387,7 +8387,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>83</v>
       </c>
@@ -8403,7 +8403,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -8455,9 +8455,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -8475,9 +8475,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -8495,9 +8495,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -8515,9 +8515,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -8533,7 +8533,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -8565,7 +8565,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -8639,7 +8639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8">
         <v>3</v>
       </c>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8">
         <v>3</v>
       </c>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>19</v>
       </c>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>19</v>
       </c>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>19</v>
       </c>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>19</v>
       </c>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="H42" s="9"/>
     </row>
-    <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>19</v>
       </c>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>19</v>
       </c>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="H44" s="9"/>
     </row>
-    <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>19</v>
       </c>
@@ -9334,19 +9334,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B357225-B76F-4ED0-9AB9-804D72D7496E}">
   <dimension ref="A1:AMJ32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -9364,7 +9364,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>91</v>
       </c>
@@ -9380,7 +9380,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -9432,9 +9432,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
@@ -9452,9 +9452,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>93</v>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -9494,7 +9494,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -9526,7 +9526,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="8">
         <v>2</v>
       </c>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="H23" s="9"/>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>19</v>
       </c>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -10022,19 +10022,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D100EB-1D85-4E6B-A54A-F3CB2CFD06DD}">
   <dimension ref="A1:AMJ34"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -10052,7 +10052,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>99</v>
       </c>
@@ -10068,7 +10068,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -10120,9 +10120,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -10140,9 +10140,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -10160,9 +10160,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -10180,9 +10180,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -10198,7 +10198,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -10230,7 +10230,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -10516,7 +10516,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
@@ -10722,16 +10722,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -10739,6 +10738,7 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -10758,19 +10758,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2BB552-8644-4710-B352-69472253D1F3}">
   <dimension ref="A1:AMJ45"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -10788,7 +10788,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>108</v>
       </c>
@@ -10804,7 +10804,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -10856,9 +10856,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -10876,9 +10876,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -10896,9 +10896,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -10916,9 +10916,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -10934,7 +10934,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -10966,7 +10966,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -11252,7 +11252,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" s="11" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8">
         <v>3</v>
       </c>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8">
         <v>3</v>
       </c>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>19</v>
       </c>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>19</v>
       </c>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>19</v>
       </c>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>19</v>
       </c>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="H42" s="9"/>
     </row>
-    <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>19</v>
       </c>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>19</v>
       </c>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="H44" s="9"/>
     </row>
-    <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>19</v>
       </c>
@@ -11735,19 +11735,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5060EA-2548-4AD8-BD83-372B0C4F7191}">
   <dimension ref="A1:AMJ34"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
-    <col min="5" max="7" width="34.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="14" customWidth="1"/>
-    <col min="9" max="1024" width="11.42578125" style="11"/>
-    <col min="1025" max="16384" width="11.42578125" style="13"/>
+    <col min="5" max="7" width="34.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="14" customWidth="1"/>
+    <col min="9" max="1024" width="11.5" style="11"/>
+    <col min="1025" max="16384" width="11.5" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -11765,7 +11765,7 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="29" t="s">
         <v>117</v>
       </c>
@@ -11781,7 +11781,7 @@
       <c r="G2" s="30"/>
       <c r="H2" s="30"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -11833,9 +11833,9 @@
       </c>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>48</v>
@@ -11853,9 +11853,9 @@
       </c>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>50</v>
@@ -11873,9 +11873,9 @@
       </c>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>84</v>
@@ -11893,9 +11893,9 @@
       </c>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>85</v>
@@ -11911,7 +11911,7 @@
       <c r="G9" s="31"/>
       <c r="H9" s="32"/>
     </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="11" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -11943,7 +11943,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="H13" s="9"/>
     </row>
-    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="H16" s="9"/>
     </row>
-    <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="H19" s="9"/>
     </row>
-    <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="H20" s="9"/>
     </row>
-    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="H21" s="9"/>
     </row>
-    <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="H22" s="9"/>
     </row>
-    <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="8">
         <v>2</v>
       </c>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="H24" s="9"/>
     </row>
-    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -12229,7 +12229,7 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8">
         <v>2</v>
       </c>
@@ -12241,13 +12241,13 @@
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>19</v>
       </c>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>19</v>
       </c>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>19</v>
       </c>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="H32" s="9"/>
     </row>
-    <row r="33" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="H33" s="9"/>
     </row>
-    <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>19</v>
       </c>

--- a/data/human/adult/validation/Scenarios/Hemorrhage/Hemorrhage.xlsx
+++ b/data/human/adult/validation/Scenarios/Hemorrhage/Hemorrhage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\Hemorrhage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A98A4C3-F087-4D2B-9E95-03DBDAC1D26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07761E42-C895-43BD-821D-7E51FC925B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="883" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="883" firstSheet="6" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class1Femoral" sheetId="15" r:id="rId1"/>
@@ -48,9 +48,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -779,9 +776,6 @@
     <t>Run for 20000s.</t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 1, "Unit": "s" }}}}</t>
-  </si>
-  <si>
     <t>Configuration</t>
   </si>
   <si>
@@ -885,6 +879,9 @@
   </si>
   <si>
     <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 5, "Unit": "s" }}}}</t>
+  </si>
+  <si>
+    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 20000, "Unit": "s" }}}}</t>
   </si>
 </sst>
 </file>
@@ -1129,6 +1126,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1153,9 +1165,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1170,18 +1179,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1587,50 +1584,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1642,11 +1639,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -1665,14 +1662,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -1687,12 +1684,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -1707,46 +1704,46 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1758,13 +1755,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -1772,13 +1769,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>65</v>
       </c>
@@ -1788,13 +1785,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>64</v>
       </c>
@@ -1811,13 +1808,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>6</v>
@@ -1837,7 +1834,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -1859,7 +1856,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -1881,7 +1878,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -1901,7 +1898,7 @@
         <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>39</v>
@@ -1923,7 +1920,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -1945,7 +1942,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -1965,7 +1962,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>39</v>
@@ -1980,13 +1977,13 @@
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="1" t="s">
         <v>6</v>
       </c>
@@ -1998,13 +1995,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="9" t="s">
         <v>46</v>
       </c>
@@ -2014,13 +2011,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>66</v>
       </c>
@@ -2037,13 +2034,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>6</v>
@@ -2063,7 +2060,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -2083,7 +2080,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -2103,7 +2100,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -2123,7 +2120,7 @@
         <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -2143,7 +2140,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -2163,7 +2160,7 @@
         <v>34</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -2183,7 +2180,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -2194,17 +2191,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B22:F22"/>
@@ -2216,6 +2202,17 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2243,50 +2240,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2298,11 +2295,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -2326,7 +2323,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -2343,12 +2340,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -2363,12 +2360,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -2383,12 +2380,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -2403,22 +2400,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2430,13 +2427,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -2444,13 +2441,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>94</v>
       </c>
@@ -2460,13 +2457,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>96</v>
       </c>
@@ -2476,13 +2473,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>112</v>
       </c>
@@ -2492,13 +2489,13 @@
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
       <c r="G15" s="1" t="s">
         <v>6</v>
       </c>
@@ -2510,13 +2507,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>70</v>
       </c>
@@ -2526,13 +2523,13 @@
       <c r="A17" s="8">
         <v>2</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
     </row>
@@ -2540,13 +2537,13 @@
       <c r="A18" s="8">
         <v>2</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="9" t="s">
         <v>214</v>
       </c>
@@ -2556,12 +2553,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -2571,15 +2571,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2601,50 +2598,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2656,11 +2653,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -2684,7 +2681,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -2701,12 +2698,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -2721,44 +2718,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2770,13 +2767,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -2784,13 +2781,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -2800,13 +2797,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
@@ -2816,13 +2813,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2834,13 +2831,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -2850,13 +2847,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -2866,12 +2863,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -2881,13 +2879,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2909,50 +2906,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2964,11 +2961,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -2992,7 +2989,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -3009,12 +3006,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -3029,44 +3026,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3078,13 +3075,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3092,13 +3089,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -3108,13 +3105,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>134</v>
       </c>
@@ -3124,13 +3121,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -3142,13 +3139,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -3158,13 +3155,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -3174,12 +3171,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -3189,13 +3187,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3217,50 +3214,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3272,11 +3269,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -3300,7 +3297,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -3317,12 +3314,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -3337,44 +3334,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3386,13 +3383,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3400,13 +3397,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -3416,13 +3413,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>133</v>
       </c>
@@ -3432,13 +3429,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -3450,13 +3447,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -3466,13 +3463,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -3482,12 +3479,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -3497,13 +3495,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3525,50 +3522,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3580,11 +3577,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -3608,7 +3605,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -3625,12 +3622,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -3645,44 +3642,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3694,13 +3691,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3708,13 +3705,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -3724,13 +3721,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>130</v>
       </c>
@@ -3740,13 +3737,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -3758,13 +3755,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -3774,13 +3771,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -3790,12 +3787,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -3805,13 +3803,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3833,50 +3830,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3888,11 +3885,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -3916,7 +3913,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -3933,12 +3930,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -3953,44 +3950,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4002,13 +3999,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -4016,13 +4013,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -4032,13 +4029,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>129</v>
       </c>
@@ -4048,13 +4045,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -4066,13 +4063,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -4082,13 +4079,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -4098,12 +4095,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -4113,13 +4111,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4141,50 +4138,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4196,11 +4193,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -4224,7 +4221,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -4241,12 +4238,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -4261,44 +4258,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4310,13 +4307,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -4324,13 +4321,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>103</v>
       </c>
@@ -4340,13 +4337,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>127</v>
       </c>
@@ -4356,13 +4353,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -4374,13 +4371,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
         <v>70</v>
       </c>
@@ -4390,13 +4387,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="B16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>215</v>
       </c>
@@ -4406,12 +4403,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -4421,13 +4419,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4449,50 +4446,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4504,11 +4501,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -4532,7 +4529,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -4549,12 +4546,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -4569,44 +4566,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4618,13 +4615,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -4632,13 +4629,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="9" t="s">
         <v>145</v>
       </c>
@@ -4648,13 +4645,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>144</v>
       </c>
@@ -4662,14 +4659,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
@@ -4681,6 +4670,14 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4704,50 +4701,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4759,11 +4756,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -4787,7 +4784,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -4804,12 +4801,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -4824,44 +4821,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4873,13 +4870,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -4887,13 +4884,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="9" t="s">
         <v>145</v>
       </c>
@@ -4905,13 +4902,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>149</v>
       </c>
@@ -4921,13 +4918,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -4939,13 +4936,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="9" t="s">
         <v>150</v>
       </c>
@@ -4955,13 +4952,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>149</v>
       </c>
@@ -4978,13 +4975,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -5004,7 +5001,7 @@
         <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -5019,13 +5016,13 @@
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="1" t="s">
         <v>6</v>
       </c>
@@ -5037,13 +5034,13 @@
       <c r="A20" s="8">
         <v>3</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="26"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="30"/>
       <c r="G20" s="9" t="s">
         <v>155</v>
       </c>
@@ -5053,13 +5050,13 @@
       <c r="A21" s="8">
         <v>3</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="9" t="s">
         <v>149</v>
       </c>
@@ -5076,13 +5073,13 @@
         <v>11</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>6</v>
@@ -5102,7 +5099,7 @@
         <v>43</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -5117,13 +5114,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -5135,13 +5132,13 @@
       <c r="A25" s="8">
         <v>4</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="26"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="30"/>
       <c r="G25" s="9" t="s">
         <v>156</v>
       </c>
@@ -5151,13 +5148,13 @@
       <c r="A26" s="8">
         <v>4</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>149</v>
       </c>
@@ -5174,13 +5171,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
@@ -5200,7 +5197,7 @@
         <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -5215,13 +5212,13 @@
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
       <c r="G29" s="1" t="s">
         <v>6</v>
       </c>
@@ -5233,13 +5230,13 @@
       <c r="A30" s="8">
         <v>5</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="26"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30"/>
       <c r="G30" s="9" t="s">
         <v>145</v>
       </c>
@@ -5249,13 +5246,13 @@
       <c r="A31" s="8">
         <v>5</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
       <c r="G31" s="9" t="s">
         <v>149</v>
       </c>
@@ -5272,13 +5269,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -5298,7 +5295,7 @@
         <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -5311,26 +5308,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B30:F30"/>
@@ -5342,6 +5319,26 @@
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5363,50 +5360,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -5418,11 +5415,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -5446,7 +5443,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -5463,12 +5460,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -5483,44 +5480,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5532,13 +5529,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -5546,13 +5543,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="9" t="s">
         <v>145</v>
       </c>
@@ -5562,13 +5559,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>149</v>
       </c>
@@ -5578,13 +5575,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -5596,13 +5593,13 @@
       <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="9" t="s">
         <v>165</v>
       </c>
@@ -5612,13 +5609,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>149</v>
       </c>
@@ -5628,13 +5625,13 @@
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="1" t="s">
         <v>6</v>
       </c>
@@ -5646,13 +5643,13 @@
       <c r="A18" s="8">
         <v>3</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="26"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="9" t="s">
         <v>165</v>
       </c>
@@ -5662,13 +5659,13 @@
       <c r="A19" s="8">
         <v>3</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="9" t="s">
         <v>149</v>
       </c>
@@ -5676,12 +5673,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -5691,16 +5692,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5724,50 +5721,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -5779,11 +5776,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -5802,14 +5799,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -5824,12 +5821,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -5844,46 +5841,46 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5895,13 +5892,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -5909,13 +5906,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>62</v>
       </c>
@@ -5925,13 +5922,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>61</v>
       </c>
@@ -5948,13 +5945,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>6</v>
@@ -5974,7 +5971,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -5996,7 +5993,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -6018,7 +6015,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -6060,7 +6057,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -6082,7 +6079,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -6102,7 +6099,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>39</v>
@@ -6117,13 +6114,13 @@
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="1" t="s">
         <v>6</v>
       </c>
@@ -6135,13 +6132,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="9" t="s">
         <v>46</v>
       </c>
@@ -6151,13 +6148,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>63</v>
       </c>
@@ -6174,13 +6171,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>6</v>
@@ -6200,7 +6197,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>39</v>
@@ -6222,7 +6219,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>39</v>
@@ -6244,7 +6241,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -6264,7 +6261,7 @@
         <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -6286,7 +6283,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>39</v>
@@ -6308,7 +6305,7 @@
         <v>34</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -6328,7 +6325,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -6339,6 +6336,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B10:F10"/>
@@ -6351,16 +6358,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6387,50 +6384,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -6442,11 +6439,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -6470,7 +6467,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -6487,12 +6484,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -6507,12 +6504,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -6527,10 +6524,10 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -6545,22 +6542,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6572,13 +6569,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -6586,13 +6583,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="9" t="s">
         <v>174</v>
       </c>
@@ -6602,13 +6599,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="9" t="s">
         <v>175</v>
       </c>
@@ -6618,13 +6615,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>149</v>
       </c>
@@ -6634,13 +6631,13 @@
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
       <c r="G15" s="1" t="s">
         <v>6</v>
       </c>
@@ -6652,13 +6649,13 @@
       <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="26"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="9" t="s">
         <v>156</v>
       </c>
@@ -6668,13 +6665,13 @@
       <c r="A17" s="8">
         <v>2</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="26"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="9" t="s">
         <v>156</v>
       </c>
@@ -6684,13 +6681,13 @@
       <c r="A18" s="8">
         <v>2</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="9" t="s">
         <v>63</v>
       </c>
@@ -6698,12 +6695,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -6713,15 +6713,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6743,50 +6740,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -6798,11 +6795,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -6826,7 +6823,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -6843,12 +6840,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -6863,44 +6860,44 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -6912,13 +6909,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -6926,13 +6923,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
       <c r="G12" s="9" t="s">
         <v>207</v>
       </c>
@@ -6942,13 +6939,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>115</v>
       </c>
@@ -6958,13 +6955,13 @@
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="1" t="s">
         <v>6</v>
       </c>
@@ -6976,13 +6973,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="9" t="s">
         <v>46</v>
       </c>
@@ -6992,13 +6989,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
         <v>63</v>
       </c>
@@ -7006,12 +7003,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G5:H5"/>
@@ -7021,13 +7019,12 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7051,50 +7048,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -7106,11 +7103,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -7129,14 +7126,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -7151,12 +7148,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -7171,12 +7168,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -7191,12 +7188,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -7211,10 +7208,10 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -7229,10 +7226,10 @@
       <c r="D10" s="2">
         <v>4</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -7247,10 +7244,10 @@
       <c r="D11" s="2">
         <v>4</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -7265,10 +7262,10 @@
       <c r="D12" s="2">
         <v>4</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -7283,10 +7280,10 @@
       <c r="D13" s="2">
         <v>4</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -7301,10 +7298,10 @@
       <c r="D14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -7319,10 +7316,10 @@
       <c r="D15" s="2">
         <v>4</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -7337,10 +7334,10 @@
       <c r="D16" s="2">
         <v>4</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
@@ -7355,10 +7352,10 @@
       <c r="D17" s="2">
         <v>4</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
@@ -7373,10 +7370,10 @@
       <c r="D18" s="2">
         <v>4</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -7391,10 +7388,10 @@
       <c r="D19" s="2">
         <v>4</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -7409,10 +7406,10 @@
       <c r="D20" s="2">
         <v>4</v>
       </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -7427,22 +7424,22 @@
       <c r="D21" s="2">
         <v>4</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="1" t="s">
         <v>6</v>
       </c>
@@ -7454,13 +7451,13 @@
       <c r="A23" s="8">
         <v>1</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="30"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -7468,13 +7465,13 @@
       <c r="A24" s="8">
         <v>1</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>87</v>
       </c>
@@ -7484,13 +7481,13 @@
       <c r="A25" s="8">
         <v>1</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9" t="s">
         <v>194</v>
       </c>
@@ -7500,13 +7497,13 @@
       <c r="A26" s="8">
         <v>1</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>195</v>
       </c>
@@ -7516,13 +7513,13 @@
       <c r="A27" s="8">
         <v>1</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
         <v>66</v>
       </c>
@@ -7532,13 +7529,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -7550,13 +7547,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9" t="s">
         <v>196</v>
       </c>
@@ -7566,13 +7563,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="9" t="s">
         <v>197</v>
       </c>
@@ -7582,13 +7579,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
       <c r="G31" s="9" t="s">
         <v>198</v>
       </c>
@@ -7598,13 +7595,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
       <c r="G32" s="9" t="s">
         <v>63</v>
       </c>
@@ -7612,6 +7609,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="G6:H21"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
@@ -7628,28 +7647,6 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7673,50 +7670,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -7728,11 +7725,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -7751,14 +7748,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -7773,12 +7770,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -7793,12 +7790,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -7813,12 +7810,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -7833,22 +7830,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -7860,13 +7857,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -7874,13 +7871,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>59</v>
       </c>
@@ -7890,13 +7887,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>60</v>
       </c>
@@ -7906,13 +7903,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>68</v>
       </c>
@@ -7929,13 +7926,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -7955,7 +7952,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -7977,7 +7974,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -7999,7 +7996,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -8041,7 +8038,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -8063,7 +8060,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -8083,7 +8080,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -8098,13 +8095,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -8116,13 +8113,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>70</v>
       </c>
@@ -8132,13 +8129,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -8146,13 +8143,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>72</v>
       </c>
@@ -8162,13 +8159,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
         <v>63</v>
       </c>
@@ -8185,13 +8182,13 @@
         <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>6</v>
@@ -8211,7 +8208,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>91</v>
@@ -8233,7 +8230,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>39</v>
@@ -8255,7 +8252,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -8275,7 +8272,7 @@
         <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>39</v>
@@ -8297,7 +8294,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>39</v>
@@ -8319,7 +8316,7 @@
         <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -8339,7 +8336,7 @@
         <v>32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -8350,6 +8347,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
@@ -8363,18 +8372,6 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -8403,50 +8400,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -8458,11 +8455,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -8481,14 +8478,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -8503,12 +8500,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -8523,12 +8520,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -8543,12 +8540,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -8563,22 +8560,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -8590,13 +8587,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -8604,13 +8601,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>59</v>
       </c>
@@ -8620,13 +8617,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>60</v>
       </c>
@@ -8636,13 +8633,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>68</v>
       </c>
@@ -8659,13 +8656,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -8685,7 +8682,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -8707,7 +8704,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -8729,7 +8726,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -8771,7 +8768,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -8793,7 +8790,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -8813,7 +8810,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -8828,13 +8825,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -8846,13 +8843,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>70</v>
       </c>
@@ -8862,13 +8859,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -8876,13 +8873,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>80</v>
       </c>
@@ -8899,13 +8896,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
@@ -8925,7 +8922,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>39</v>
@@ -8947,7 +8944,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -8969,7 +8966,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -8989,7 +8986,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>39</v>
@@ -9011,7 +9008,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>39</v>
@@ -9033,7 +9030,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -9053,7 +9050,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -9066,13 +9063,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -9084,13 +9081,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9" t="s">
         <v>82</v>
       </c>
@@ -9100,13 +9097,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9" t="s">
         <v>63</v>
       </c>
@@ -9123,13 +9120,13 @@
         <v>11</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>6</v>
@@ -9149,7 +9146,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>91</v>
@@ -9171,7 +9168,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>39</v>
@@ -9193,7 +9190,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -9213,7 +9210,7 @@
         <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>39</v>
@@ -9235,7 +9232,7 @@
         <v>19</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>39</v>
@@ -9257,7 +9254,7 @@
         <v>34</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -9277,7 +9274,7 @@
         <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -9288,6 +9285,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
@@ -9304,17 +9312,6 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -9343,50 +9340,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -9398,11 +9395,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -9421,14 +9418,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -9443,12 +9440,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -9463,46 +9460,46 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -9514,13 +9511,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -9528,13 +9525,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>87</v>
       </c>
@@ -9544,13 +9541,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>115</v>
       </c>
@@ -9567,13 +9564,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>6</v>
@@ -9593,7 +9590,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>39</v>
@@ -9615,7 +9612,7 @@
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -9637,7 +9634,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -9679,7 +9676,7 @@
         <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -9701,7 +9698,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -9721,7 +9718,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>39</v>
@@ -9736,13 +9733,13 @@
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
       <c r="G22" s="1" t="s">
         <v>6</v>
       </c>
@@ -9754,13 +9751,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="9" t="s">
         <v>46</v>
       </c>
@@ -9770,13 +9767,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>63</v>
       </c>
@@ -9793,13 +9790,13 @@
         <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>6</v>
@@ -9819,7 +9816,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>39</v>
@@ -9841,7 +9838,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>39</v>
@@ -9863,7 +9860,7 @@
         <v>19</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -9883,7 +9880,7 @@
         <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -9905,7 +9902,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>39</v>
@@ -9927,7 +9924,7 @@
         <v>34</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -9947,7 +9944,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -9958,13 +9955,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
@@ -9980,6 +9970,13 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10008,50 +10005,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -10063,11 +10060,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -10086,14 +10083,14 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -10108,12 +10105,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -10128,12 +10125,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -10148,12 +10145,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -10168,22 +10165,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10195,13 +10192,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -10209,13 +10206,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>94</v>
       </c>
@@ -10225,13 +10222,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>96</v>
       </c>
@@ -10241,13 +10238,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>98</v>
       </c>
@@ -10264,13 +10261,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -10290,7 +10287,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -10312,7 +10309,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -10334,7 +10331,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -10354,7 +10351,7 @@
         <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -10376,7 +10373,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -10398,7 +10395,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -10418,7 +10415,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -10433,13 +10430,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -10451,13 +10448,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>70</v>
       </c>
@@ -10467,13 +10464,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -10481,13 +10478,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>66</v>
       </c>
@@ -10504,13 +10501,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
@@ -10530,7 +10527,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>39</v>
@@ -10552,7 +10549,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -10574,7 +10571,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -10594,7 +10591,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>39</v>
@@ -10616,7 +10613,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>39</v>
@@ -10638,7 +10635,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -10658,7 +10655,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -10669,15 +10666,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
@@ -10693,6 +10681,15 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10721,50 +10718,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -10776,11 +10773,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -10803,10 +10800,10 @@
         <v>13</v>
       </c>
       <c r="F5" s="34"/>
-      <c r="G5" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="29"/>
+      <c r="G5" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -10821,12 +10818,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -10841,12 +10838,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -10861,12 +10858,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -10881,22 +10878,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -10908,13 +10905,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -10922,13 +10919,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>94</v>
       </c>
@@ -10938,13 +10935,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>103</v>
       </c>
@@ -10954,13 +10951,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>63</v>
       </c>
@@ -10977,13 +10974,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -11003,7 +11000,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -11025,7 +11022,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -11047,7 +11044,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -11067,7 +11064,7 @@
         <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -11089,7 +11086,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -11111,7 +11108,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -11131,7 +11128,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -11146,13 +11143,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -11164,13 +11161,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>70</v>
       </c>
@@ -11180,13 +11177,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -11194,13 +11191,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>80</v>
       </c>
@@ -11217,13 +11214,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
@@ -11243,7 +11240,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>39</v>
@@ -11265,7 +11262,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -11287,7 +11284,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -11307,7 +11304,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>39</v>
@@ -11329,7 +11326,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>39</v>
@@ -11351,7 +11348,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -11371,7 +11368,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -11384,13 +11381,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -11402,13 +11399,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9" t="s">
         <v>108</v>
       </c>
@@ -11418,13 +11415,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9" t="s">
         <v>106</v>
       </c>
@@ -11441,13 +11438,13 @@
         <v>11</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>6</v>
@@ -11467,7 +11464,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
@@ -11487,7 +11484,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>39</v>
@@ -11509,7 +11506,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -11529,7 +11526,7 @@
         <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>39</v>
@@ -11551,7 +11548,7 @@
         <v>19</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>39</v>
@@ -11573,7 +11570,7 @@
         <v>34</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -11593,7 +11590,7 @@
         <v>32</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>39</v>
@@ -11606,18 +11603,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
@@ -11633,6 +11618,18 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -11661,50 +11658,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -11716,11 +11713,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="9" t="s">
         <v>8</v>
@@ -11744,7 +11741,7 @@
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H5" s="34"/>
     </row>
@@ -11761,12 +11758,12 @@
       <c r="D6" s="2">
         <v>4</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11781,12 +11778,12 @@
       <c r="D7" s="2">
         <v>4</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -11801,12 +11798,12 @@
       <c r="D8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="28"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -11821,22 +11818,22 @@
       <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -11848,13 +11845,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -11862,13 +11859,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>94</v>
       </c>
@@ -11878,13 +11875,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>96</v>
       </c>
@@ -11894,13 +11891,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
         <v>112</v>
       </c>
@@ -11917,13 +11914,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -11943,7 +11940,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>39</v>
@@ -11965,7 +11962,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>39</v>
@@ -11987,7 +11984,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -12007,7 +12004,7 @@
         <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -12029,7 +12026,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -12051,7 +12048,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -12071,7 +12068,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -12086,13 +12083,13 @@
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
       <c r="G23" s="1" t="s">
         <v>6</v>
       </c>
@@ -12104,13 +12101,13 @@
       <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="9" t="s">
         <v>70</v>
       </c>
@@ -12120,13 +12117,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -12134,13 +12131,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="B26" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>135</v>
       </c>
@@ -12159,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>6</v>
@@ -12185,7 +12182,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>39</v>
@@ -12207,7 +12204,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>39</v>
@@ -12229,7 +12226,7 @@
         <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -12249,7 +12246,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>39</v>
@@ -12271,7 +12268,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>39</v>
@@ -12293,7 +12290,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -12313,7 +12310,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -12324,6 +12321,21 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
@@ -12333,21 +12345,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
